--- a/curation/package16/R16_BC_SDTM_VS.xlsx
+++ b/curation/package16/R16_BC_SDTM_VS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package16\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\package16\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BAE2D2-3C50-4524-80B4-052583893B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B49441-84AE-4DE4-9F41-B9F449BDDCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_VS" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12196" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12197" uniqueCount="556">
   <si>
     <t>package_date</t>
   </si>
@@ -1932,9 +1932,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1954,6 +1951,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2524,7 +2524,7 @@
       <c r="E9" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>409</v>
       </c>
       <c r="I9" s="4" t="s">
@@ -4068,7 +4068,7 @@
       <c r="K44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L44" s="12" t="s">
+      <c r="L44" s="11" t="s">
         <v>529</v>
       </c>
       <c r="M44" s="4" t="s">
@@ -4118,7 +4118,7 @@
       <c r="K45" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L45" s="12" t="s">
+      <c r="L45" s="11" t="s">
         <v>529</v>
       </c>
       <c r="M45" s="4" t="s">
@@ -4171,7 +4171,7 @@
       <c r="K46" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L46" s="12" t="s">
+      <c r="L46" s="11" t="s">
         <v>529</v>
       </c>
       <c r="M46" s="4" t="s">
@@ -4221,7 +4221,7 @@
       <c r="K47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L47" s="12" t="s">
+      <c r="L47" s="11" t="s">
         <v>530</v>
       </c>
       <c r="M47" s="4" t="s">
@@ -4271,7 +4271,7 @@
       <c r="K48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L48" s="12" t="s">
+      <c r="L48" s="11" t="s">
         <v>530</v>
       </c>
       <c r="M48" s="4" t="s">
@@ -4324,7 +4324,7 @@
       <c r="K49" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L49" s="12" t="s">
+      <c r="L49" s="11" t="s">
         <v>530</v>
       </c>
       <c r="M49" s="4" t="s">
@@ -4394,28 +4394,28 @@
       <c r="A51" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="12" t="s">
         <v>115</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="12" t="s">
         <v>116</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I51" s="13" t="s">
+      <c r="I51" s="12" t="s">
         <v>117</v>
       </c>
       <c r="J51" s="4" t="s">
@@ -4427,19 +4427,19 @@
       <c r="L51" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="M51" s="13" t="s">
+      <c r="M51" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="N51" s="13" t="s">
+      <c r="N51" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="O51" s="13" t="s">
+      <c r="O51" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="P51" s="13" t="s">
+      <c r="P51" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="Q51" s="14" t="s">
+      <c r="Q51" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       <c r="E79" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F79" s="13" t="s">
+      <c r="F79" s="12" t="s">
         <v>409</v>
       </c>
       <c r="G79" s="4" t="s">
@@ -5728,7 +5728,7 @@
       <c r="E80" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="12" t="s">
         <v>409</v>
       </c>
       <c r="G80" s="4" t="s">
@@ -5781,7 +5781,7 @@
       <c r="E81" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F81" s="13" t="s">
+      <c r="F81" s="12" t="s">
         <v>409</v>
       </c>
       <c r="G81" s="4" t="s">
@@ -6535,7 +6535,7 @@
       <c r="K98" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L98" s="12" t="s">
+      <c r="L98" s="11" t="s">
         <v>531</v>
       </c>
       <c r="M98" s="4" t="s">
@@ -6585,7 +6585,7 @@
       <c r="K99" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L99" s="12" t="s">
+      <c r="L99" s="11" t="s">
         <v>531</v>
       </c>
       <c r="M99" s="4" t="s">
@@ -6638,7 +6638,7 @@
       <c r="K100" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L100" s="12" t="s">
+      <c r="L100" s="11" t="s">
         <v>531</v>
       </c>
       <c r="M100" s="4" t="s">
@@ -6685,8 +6685,8 @@
       <c r="K101" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L101" s="11">
-        <v>2333537</v>
+      <c r="L101" s="18" t="s">
+        <v>223</v>
       </c>
       <c r="M101" s="4" t="s">
         <v>22</v>
@@ -7319,7 +7319,7 @@
       <c r="P115" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q115" s="15" t="s">
+      <c r="Q115" s="14" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       <c r="K120" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L120" s="12" t="s">
+      <c r="L120" s="11" t="s">
         <v>532</v>
       </c>
       <c r="M120" s="4" t="s">
@@ -7583,7 +7583,7 @@
       <c r="K121" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L121" s="12" t="s">
+      <c r="L121" s="11" t="s">
         <v>532</v>
       </c>
       <c r="M121" s="4" t="s">
@@ -7598,7 +7598,7 @@
       <c r="P121" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q121" s="15" t="s">
+      <c r="Q121" s="14" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       <c r="K122" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L122" s="12" t="s">
+      <c r="L122" s="11" t="s">
         <v>532</v>
       </c>
       <c r="M122" s="4" t="s">
@@ -7859,7 +7859,7 @@
       <c r="P127" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q127" s="15" t="s">
+      <c r="Q127" s="14" t="s">
         <v>73</v>
       </c>
     </row>
@@ -7911,10 +7911,10 @@
       <c r="B129" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C129" s="16" t="s">
+      <c r="C129" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D129" s="16" t="s">
+      <c r="D129" s="15" t="s">
         <v>182</v>
       </c>
       <c r="F129" s="4" t="s">
@@ -7949,10 +7949,10 @@
       <c r="B130" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="16" t="s">
+      <c r="C130" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D130" s="16" t="s">
+      <c r="D130" s="15" t="s">
         <v>182</v>
       </c>
       <c r="F130" s="4" t="s">
@@ -7990,10 +7990,10 @@
       <c r="B131" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C131" s="16" t="s">
+      <c r="C131" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D131" s="16" t="s">
+      <c r="D131" s="15" t="s">
         <v>182</v>
       </c>
       <c r="F131" s="4" t="s">
@@ -10196,7 +10196,7 @@
       <c r="K181" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L181" s="12" t="s">
+      <c r="L181" s="11" t="s">
         <v>533</v>
       </c>
       <c r="M181" s="4" t="s">
@@ -10243,7 +10243,7 @@
       <c r="K182" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L182" s="12" t="s">
+      <c r="L182" s="11" t="s">
         <v>533</v>
       </c>
       <c r="M182" s="4" t="s">
@@ -41491,622 +41491,622 @@
       </c>
     </row>
     <row r="2" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G2" s="17" t="s">
+      <c r="C2" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L2" s="18" t="s">
+      <c r="I2" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L2" s="17" t="s">
         <v>442</v>
       </c>
-      <c r="M2" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17" t="s">
+      <c r="M2" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="16" t="s">
         <v>443</v>
       </c>
-      <c r="S2" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="T2" s="17" t="s">
+      <c r="S2" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="T2" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="U2" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="V2" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AB2" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17" t="s">
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB2" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
     </row>
     <row r="3" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="C3" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L3" s="18" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17" t="s">
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="V3" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AB3" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17"/>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="17"/>
+      <c r="V3" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB3" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G4" s="17" t="s">
+      <c r="C4" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17" t="s">
+      <c r="K4" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="S4" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="T4" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="V4" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="W4" s="17" t="s">
+      <c r="V4" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="W4" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="X4" s="17">
+      <c r="X4" s="16">
         <v>8</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="Y4" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="Z4" s="17">
+      <c r="Z4" s="16">
         <v>3</v>
       </c>
-      <c r="AA4" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AB4" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC4" s="17" t="s">
+      <c r="AA4" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB4" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC4" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="AD4" s="17" t="s">
+      <c r="AD4" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG4" s="17" t="s">
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG4" s="16" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="C5" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L5" s="18" t="s">
+      <c r="K5" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="16" t="s">
         <v>551</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="N5" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="O5" s="16" t="s">
         <v>553</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17" t="s">
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="S5" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="T5" s="17" t="s">
+      <c r="T5" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="U5" s="17" t="s">
+      <c r="U5" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="V5" s="17" t="s">
+      <c r="V5" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AB5" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG5" s="17"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB5" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG5" s="16"/>
     </row>
     <row r="6" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="C6" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17" t="s">
+      <c r="K6" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S6" s="17" t="s">
+      <c r="S6" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="T6" s="17" t="s">
+      <c r="T6" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="U6" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="V6" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="W6" s="17" t="s">
+      <c r="V6" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="W6" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="X6" s="17">
+      <c r="X6" s="16">
         <v>8</v>
       </c>
-      <c r="Y6" s="17" t="s">
+      <c r="Y6" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="Z6" s="17">
+      <c r="Z6" s="16">
         <v>3</v>
       </c>
-      <c r="AA6" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AB6" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG6" s="17"/>
+      <c r="AA6" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG6" s="16"/>
     </row>
     <row r="7" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="C7" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17" t="s">
+      <c r="K7" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="S7" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="T7" s="17" t="s">
+      <c r="T7" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="U7" s="17" t="s">
+      <c r="U7" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="V7" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="W7" s="17" t="s">
+      <c r="V7" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="W7" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="X7" s="17">
+      <c r="X7" s="16">
         <v>8</v>
       </c>
-      <c r="Y7" s="17" t="s">
+      <c r="Y7" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="Z7" s="17">
+      <c r="Z7" s="16">
         <v>3</v>
       </c>
-      <c r="AA7" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AB7" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG7" s="17"/>
+      <c r="AA7" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB7" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG7" s="16"/>
     </row>
     <row r="8" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="C8" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L8" s="18" t="s">
+      <c r="K8" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L8" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="16" t="s">
         <v>460</v>
       </c>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17" t="s">
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="S8" s="17" t="s">
+      <c r="S8" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="T8" s="17" t="s">
+      <c r="T8" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="U8" s="17" t="s">
+      <c r="U8" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="V8" s="17" t="s">
+      <c r="V8" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AB8" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG8" s="17"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG8" s="16"/>
     </row>
     <row r="9" spans="1:33" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="G9" s="17" t="s">
+      <c r="C9" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17" t="s">
+      <c r="K9" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16" t="s">
         <v>467</v>
       </c>
-      <c r="S9" s="17" t="s">
+      <c r="S9" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="T9" s="17" t="s">
+      <c r="T9" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="U9" s="17" t="s">
+      <c r="U9" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="V9" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="AB9" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
+      <c r="V9" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB9" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
